--- a/artfynd/A 38396-2021 artfynd.xlsx
+++ b/artfynd/A 38396-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38396-2021 artfynd.xlsx
+++ b/artfynd/A 38396-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107416687</v>
+        <v>125228086</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckdal vid kåddisvägskälet, Vb</t>
+          <t>Kåddis,brädlada, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750367.0913888238</v>
+        <v>750422</v>
       </c>
       <c r="R2" t="n">
-        <v>7090670.087548368</v>
+        <v>7090465</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-02-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-02-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,21 +767,119 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ralf Norberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ralf Norberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107416687</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bäckdal vid kåddisvägskälet, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>750367</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7090670</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2010-02-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2010-02-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Anders Engström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Anders Engström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
